--- a/Auswahl_Folientyp.xlsx
+++ b/Auswahl_Folientyp.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://aquasun-my.sharepoint.com/personal/michael_hiller_aquasun_de/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="360" documentId="8_{B33A633F-391A-4782-9980-57879B1A347E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F061D9B0-14D4-4C20-9243-BE75D99C67C9}"/>
+  <xr:revisionPtr revIDLastSave="363" documentId="8_{B33A633F-391A-4782-9980-57879B1A347E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BDE0C3C5-99C7-114C-A1E5-61D61FD1CA48}"/>
   <bookViews>
     <workbookView xWindow="1095" yWindow="135" windowWidth="40725" windowHeight="22995" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -808,29 +808,30 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q100"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="4.140625" style="5" customWidth="1"/>
-    <col min="2" max="2" width="27.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="11" width="5" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="5" customWidth="1"/>
-    <col min="14" max="15" width="6" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.16796875" style="5" customWidth="1"/>
+    <col min="2" max="2" width="27.171875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.72265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.6484375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.05078125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="6.05078125" customWidth="1"/>
+    <col min="8" max="8" width="6.05078125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.05078125" customWidth="1"/>
+    <col min="10" max="10" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.9765625" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="4.9765625" customWidth="1"/>
+    <col min="14" max="15" width="6.05078125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.35546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.76171875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
       <c r="E1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="E2" s="6">
         <v>914</v>
       </c>
@@ -865,7 +866,7 @@
         <v>1829</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B3" s="3" t="s">
         <v>42</v>
       </c>
@@ -915,7 +916,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>41</v>
       </c>
@@ -935,7 +936,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>41</v>
       </c>
@@ -949,13 +950,13 @@
         <v>19</v>
       </c>
       <c r="N5">
-        <v>1254</v>
+        <v>1524</v>
       </c>
       <c r="P5">
         <v>30480</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>45</v>
       </c>
@@ -978,7 +979,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B7" s="1" t="s">
         <v>46</v>
       </c>
@@ -1001,7 +1002,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B8" s="1" t="s">
         <v>47</v>
       </c>
@@ -1027,7 +1028,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B9" s="1" t="s">
         <v>48</v>
       </c>
@@ -1050,7 +1051,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B10" s="1" t="s">
         <v>49</v>
       </c>
@@ -1073,7 +1074,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B11" s="1" t="s">
         <v>50</v>
       </c>
@@ -1090,7 +1091,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
         <v>41</v>
       </c>
@@ -1110,7 +1111,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B13" s="1" t="s">
         <v>52</v>
       </c>
@@ -1133,7 +1134,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
         <v>53</v>
       </c>
@@ -1153,7 +1154,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B15" s="1" t="s">
         <v>54</v>
       </c>
@@ -1170,7 +1171,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
         <v>55</v>
       </c>
@@ -1193,7 +1194,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B17" s="1" t="s">
         <v>95</v>
       </c>
@@ -1213,7 +1214,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B18" s="1" t="s">
         <v>2</v>
       </c>
@@ -1230,7 +1231,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
         <v>96</v>
       </c>
@@ -1250,7 +1251,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B20" s="1" t="s">
         <v>97</v>
       </c>
@@ -1270,7 +1271,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B21" s="1" t="s">
         <v>56</v>
       </c>
@@ -1287,7 +1288,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B22" s="1" t="s">
         <v>57</v>
       </c>
@@ -1304,7 +1305,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
         <v>41</v>
       </c>
@@ -1324,7 +1325,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
         <v>41</v>
       </c>
@@ -1344,7 +1345,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B25" s="1" t="s">
         <v>98</v>
       </c>
@@ -1364,7 +1365,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B26" s="1" t="s">
         <v>99</v>
       </c>
@@ -1381,7 +1382,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B27" s="1" t="s">
         <v>4</v>
       </c>
@@ -1398,7 +1399,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B28" s="1" t="s">
         <v>5</v>
       </c>
@@ -1415,7 +1416,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
         <v>41</v>
       </c>
@@ -1435,7 +1436,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B30" s="9" t="s">
         <v>59</v>
       </c>
@@ -1461,7 +1462,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B31" s="1" t="s">
         <v>60</v>
       </c>
@@ -1481,7 +1482,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B32" s="1" t="s">
         <v>61</v>
       </c>
@@ -1501,7 +1502,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
         <v>41</v>
       </c>
@@ -1521,7 +1522,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B34" s="1" t="s">
         <v>101</v>
       </c>
@@ -1538,7 +1539,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B35" s="1" t="s">
         <v>7</v>
       </c>
@@ -1555,7 +1556,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B36" s="1" t="s">
         <v>8</v>
       </c>
@@ -1572,7 +1573,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>9</v>
       </c>
@@ -1589,7 +1590,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B38" s="1" t="s">
         <v>10</v>
       </c>
@@ -1606,7 +1607,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B39" s="1" t="s">
         <v>11</v>
       </c>
@@ -1623,7 +1624,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B40" s="1" t="s">
         <v>12</v>
       </c>
@@ -1640,7 +1641,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B41" s="1" t="s">
         <v>13</v>
       </c>
@@ -1657,7 +1658,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B42" s="1" t="s">
         <v>14</v>
       </c>
@@ -1674,7 +1675,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
         <v>41</v>
       </c>
@@ -1694,7 +1695,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B44" s="1" t="s">
         <v>16</v>
       </c>
@@ -1711,7 +1712,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B45" s="1" t="s">
         <v>17</v>
       </c>
@@ -1728,7 +1729,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B46" s="1" t="s">
         <v>18</v>
       </c>
@@ -1745,7 +1746,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B47" s="1" t="s">
         <v>19</v>
       </c>
@@ -1762,7 +1763,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B48" s="1" t="s">
         <v>20</v>
       </c>
@@ -1779,7 +1780,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B49" s="1" t="s">
         <v>21</v>
       </c>
@@ -1796,7 +1797,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
         <v>22</v>
       </c>
@@ -1816,7 +1817,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A51" s="5" t="s">
         <v>41</v>
       </c>
@@ -1836,7 +1837,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B52" s="1" t="s">
         <v>24</v>
       </c>
@@ -1856,7 +1857,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B53" s="1" t="s">
         <v>25</v>
       </c>
@@ -1873,7 +1874,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B54" s="1" t="s">
         <v>26</v>
       </c>
@@ -1890,7 +1891,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A55" s="5" t="s">
         <v>41</v>
       </c>
@@ -1910,7 +1911,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B56" s="1" t="s">
         <v>28</v>
       </c>
@@ -1930,7 +1931,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B57" s="1" t="s">
         <v>63</v>
       </c>
@@ -1947,7 +1948,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
         <v>64</v>
       </c>
@@ -1964,7 +1965,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A59" s="5" t="s">
         <v>41</v>
       </c>
@@ -1984,7 +1985,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B60" s="1" t="s">
         <v>66</v>
       </c>
@@ -2001,7 +2002,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B61" s="1" t="s">
         <v>29</v>
       </c>
@@ -2018,7 +2019,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B62" s="1" t="s">
         <v>30</v>
       </c>
@@ -2035,7 +2036,7 @@
         <v>25000</v>
       </c>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B63" s="1" t="s">
         <v>31</v>
       </c>
@@ -2052,7 +2053,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B64" s="1" t="s">
         <v>67</v>
       </c>
@@ -2075,7 +2076,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B65" s="1" t="s">
         <v>68</v>
       </c>
@@ -2098,7 +2099,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B66" s="1" t="s">
         <v>69</v>
       </c>
@@ -2121,7 +2122,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B67" s="1" t="s">
         <v>70</v>
       </c>
@@ -2144,7 +2145,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B68" s="1" t="s">
         <v>71</v>
       </c>
@@ -2161,7 +2162,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B69" s="1" t="s">
         <v>72</v>
       </c>
@@ -2184,7 +2185,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B70" s="1" t="s">
         <v>73</v>
       </c>
@@ -2201,7 +2202,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B71" s="1" t="s">
         <v>74</v>
       </c>
@@ -2218,7 +2219,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B72" s="1" t="s">
         <v>75</v>
       </c>
@@ -2235,7 +2236,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B73" s="1" t="s">
         <v>76</v>
       </c>
@@ -2255,7 +2256,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B74" s="1" t="s">
         <v>77</v>
       </c>
@@ -2275,7 +2276,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B75" s="1" t="s">
         <v>78</v>
       </c>
@@ -2298,7 +2299,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B76" s="1" t="s">
         <v>79</v>
       </c>
@@ -2318,7 +2319,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B77" s="1" t="s">
         <v>80</v>
       </c>
@@ -2335,7 +2336,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B78" s="1" t="s">
         <v>81</v>
       </c>
@@ -2352,7 +2353,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>32</v>
       </c>
@@ -2369,7 +2370,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A80" s="5" t="s">
         <v>41</v>
       </c>
@@ -2389,7 +2390,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B81" s="1" t="s">
         <v>82</v>
       </c>
@@ -2406,7 +2407,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B82" s="1" t="s">
         <v>114</v>
       </c>
@@ -2429,7 +2430,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A83" s="5" t="s">
         <v>41</v>
       </c>
@@ -2449,7 +2450,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B84" s="1" t="s">
         <v>84</v>
       </c>
@@ -2466,7 +2467,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B85" s="1" t="s">
         <v>115</v>
       </c>
@@ -2483,7 +2484,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B86" s="1" t="s">
         <v>85</v>
       </c>
@@ -2503,7 +2504,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B87" s="1" t="s">
         <v>86</v>
       </c>
@@ -2523,7 +2524,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A88" s="5" t="s">
         <v>41</v>
       </c>
@@ -2543,7 +2544,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B89" s="1" t="s">
         <v>88</v>
       </c>
@@ -2560,7 +2561,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B90" s="1" t="s">
         <v>100</v>
       </c>
@@ -2580,7 +2581,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B91" s="1" t="s">
         <v>89</v>
       </c>
@@ -2600,7 +2601,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B92" s="1" t="s">
         <v>90</v>
       </c>
@@ -2617,7 +2618,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A93" s="5" t="s">
         <v>41</v>
       </c>
@@ -2637,7 +2638,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B94" s="1" t="s">
         <v>91</v>
       </c>
@@ -2654,7 +2655,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B95" s="1" t="s">
         <v>34</v>
       </c>
@@ -2671,7 +2672,7 @@
         <v>25000</v>
       </c>
     </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B96" s="1" t="s">
         <v>35</v>
       </c>
@@ -2688,7 +2689,7 @@
         <v>25000</v>
       </c>
     </row>
-    <row r="97" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B97" s="1" t="s">
         <v>36</v>
       </c>
@@ -2702,13 +2703,13 @@
         <v>1000</v>
       </c>
       <c r="J97">
-        <v>1250</v>
+        <v>1260</v>
       </c>
       <c r="P97">
         <v>30480</v>
       </c>
     </row>
-    <row r="98" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B98" s="1" t="s">
         <v>37</v>
       </c>
@@ -2722,13 +2723,13 @@
         <v>1000</v>
       </c>
       <c r="J98">
-        <v>1250</v>
+        <v>1260</v>
       </c>
       <c r="P98">
         <v>30480</v>
       </c>
     </row>
-    <row r="99" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B99" s="1" t="s">
         <v>38</v>
       </c>
@@ -2745,7 +2746,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="100" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B100" s="1" t="s">
         <v>93</v>
       </c>

--- a/Auswahl_Folientyp.xlsx
+++ b/Auswahl_Folientyp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://aquasun-my.sharepoint.com/personal/michael_hiller_aquasun_de/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="363" documentId="8_{B33A633F-391A-4782-9980-57879B1A347E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BDE0C3C5-99C7-114C-A1E5-61D61FD1CA48}"/>
+  <xr:revisionPtr revIDLastSave="365" documentId="8_{B33A633F-391A-4782-9980-57879B1A347E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0012DB9A-DF55-5141-9FFA-E2405700D40B}"/>
   <bookViews>
     <workbookView xWindow="1095" yWindow="135" windowWidth="40725" windowHeight="22995" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2706,7 +2706,7 @@
         <v>1260</v>
       </c>
       <c r="P97">
-        <v>30480</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="98" spans="2:16" x14ac:dyDescent="0.2">
@@ -2726,7 +2726,7 @@
         <v>1260</v>
       </c>
       <c r="P98">
-        <v>30480</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="99" spans="2:16" x14ac:dyDescent="0.2">

--- a/Auswahl_Folientyp.xlsx
+++ b/Auswahl_Folientyp.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://aquasun-my.sharepoint.com/personal/michael_hiller_aquasun_de/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="365" documentId="8_{B33A633F-391A-4782-9980-57879B1A347E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0012DB9A-DF55-5141-9FFA-E2405700D40B}"/>
+  <xr:revisionPtr revIDLastSave="375" documentId="8_{B33A633F-391A-4782-9980-57879B1A347E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{91BEBAC7-EC5E-4D7C-9B65-84CE0CD1D16D}"/>
   <bookViews>
-    <workbookView xWindow="1095" yWindow="135" windowWidth="40725" windowHeight="22995" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9375" yWindow="0" windowWidth="38625" windowHeight="22995" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="116">
   <si>
     <t>Einheit</t>
   </si>
@@ -387,7 +387,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -411,6 +411,12 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0070C0"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -441,7 +447,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -464,12 +470,7 @@
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -808,30 +809,30 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q100"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.16796875" style="5" customWidth="1"/>
-    <col min="2" max="2" width="27.171875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.72265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.6484375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.05078125" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="6.05078125" customWidth="1"/>
-    <col min="8" max="8" width="6.05078125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.05078125" customWidth="1"/>
-    <col min="10" max="10" width="5.109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.9765625" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="4.9765625" customWidth="1"/>
-    <col min="14" max="15" width="6.05078125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.35546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.76171875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.140625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="27.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="6" customWidth="1"/>
+    <col min="8" max="8" width="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6" customWidth="1"/>
+    <col min="10" max="10" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="5" customWidth="1"/>
+    <col min="14" max="15" width="6" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="E1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="E2" s="6">
         <v>914</v>
       </c>
@@ -866,7 +867,7 @@
         <v>1829</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
         <v>42</v>
       </c>
@@ -916,38 +917,41 @@
         <v>102</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>41</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N4">
         <v>1524</v>
       </c>
+      <c r="O4">
+        <v>1829</v>
+      </c>
       <c r="P4">
         <v>30480</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>41</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>44</v>
+        <v>99</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="2">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="N5">
         <v>1524</v>
@@ -956,18 +960,15 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
-        <v>45</v>
+        <v>95</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D6" s="2">
-        <v>46</v>
-      </c>
-      <c r="E6">
-        <v>914</v>
+        <v>19.5</v>
       </c>
       <c r="N6">
         <v>1524</v>
@@ -979,130 +980,106 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D7" s="2">
-        <v>46</v>
-      </c>
-      <c r="E7">
-        <v>914</v>
+        <v>6.5</v>
       </c>
       <c r="N7">
         <v>1524</v>
       </c>
-      <c r="O7">
-        <v>1829</v>
-      </c>
       <c r="P7">
         <v>30480</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D8" s="2">
-        <v>46</v>
-      </c>
-      <c r="E8">
-        <v>914</v>
-      </c>
-      <c r="H8">
-        <v>1219</v>
+        <v>4.5</v>
       </c>
       <c r="N8">
         <v>1524</v>
       </c>
-      <c r="O8">
-        <v>1829</v>
-      </c>
       <c r="P8">
         <v>30480</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B9" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D9" s="2">
-        <v>45</v>
-      </c>
-      <c r="E9">
-        <v>914</v>
+        <v>19</v>
       </c>
       <c r="N9">
         <v>1524</v>
       </c>
-      <c r="O9">
-        <v>1829</v>
-      </c>
       <c r="P9">
         <v>30480</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D10" s="2">
-        <v>37</v>
-      </c>
-      <c r="E10">
-        <v>914</v>
+        <v>8.5</v>
       </c>
       <c r="N10">
         <v>1524</v>
       </c>
-      <c r="O10">
-        <v>1829</v>
-      </c>
       <c r="P10">
         <v>30480</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D11" s="2">
-        <v>20</v>
-      </c>
-      <c r="N11">
-        <v>1524</v>
+        <v>99</v>
+      </c>
+      <c r="M11">
+        <v>1500</v>
       </c>
       <c r="P11">
-        <v>30480</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="4" t="s">
-        <v>51</v>
+      <c r="B12" s="1" t="s">
+        <v>96</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D12" s="2">
-        <v>30</v>
+        <v>9</v>
+      </c>
+      <c r="H12">
+        <v>1219</v>
       </c>
       <c r="N12">
         <v>1524</v>
@@ -1111,135 +1088,123 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
-        <v>52</v>
+        <v>97</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D13" s="2">
-        <v>21.5</v>
-      </c>
-      <c r="E13">
-        <v>914</v>
+        <v>5</v>
+      </c>
+      <c r="H13">
+        <v>1219</v>
       </c>
       <c r="N13">
         <v>1524</v>
       </c>
-      <c r="O13">
+      <c r="P13">
+        <v>30480</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B14" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D14" s="2">
+        <v>12</v>
+      </c>
+      <c r="N14">
+        <v>1524</v>
+      </c>
+      <c r="P14">
+        <v>30480</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B15" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D15" s="2">
+        <v>5</v>
+      </c>
+      <c r="N15">
+        <v>1524</v>
+      </c>
+      <c r="P15">
+        <v>30480</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B16" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D16" s="2">
+        <v>99</v>
+      </c>
+      <c r="H16">
+        <v>1219</v>
+      </c>
+      <c r="P16">
+        <v>30480</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B17" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D17" s="2">
+        <v>55</v>
+      </c>
+      <c r="N17">
+        <v>1524</v>
+      </c>
+      <c r="P17">
+        <v>30480</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B18" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D18" s="2">
+        <v>3</v>
+      </c>
+      <c r="N18">
+        <v>1524</v>
+      </c>
+      <c r="O18">
         <v>1829</v>
       </c>
-      <c r="P13">
-        <v>30480</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B14" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D14" s="2">
-        <v>21.5</v>
-      </c>
-      <c r="K14">
-        <v>1270</v>
-      </c>
-      <c r="N14">
-        <v>1524</v>
-      </c>
-      <c r="P14">
-        <v>30480</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B15" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D15" s="2">
-        <v>19.5</v>
-      </c>
-      <c r="O15">
-        <v>1829</v>
-      </c>
-      <c r="P15">
-        <v>30480</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B16" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D16" s="2">
-        <v>12</v>
-      </c>
-      <c r="K16">
-        <v>1270</v>
-      </c>
-      <c r="N16">
-        <v>1524</v>
-      </c>
-      <c r="O16">
-        <v>1829</v>
-      </c>
-      <c r="P16">
-        <v>30480</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B17" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D17" s="2">
-        <v>19.5</v>
-      </c>
-      <c r="N17">
-        <v>1524</v>
-      </c>
-      <c r="O17">
-        <v>1829</v>
-      </c>
-      <c r="P17">
-        <v>30480</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B18" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D18" s="2">
-        <v>6.5</v>
-      </c>
-      <c r="N18">
-        <v>1524</v>
-      </c>
       <c r="P18">
         <v>30480</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
-        <v>96</v>
+        <v>59</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D19" s="2">
-        <v>9</v>
+      <c r="D19" s="7">
+        <v>10.5</v>
       </c>
       <c r="H19">
         <v>1219</v>
@@ -1247,19 +1212,22 @@
       <c r="N19">
         <v>1524</v>
       </c>
+      <c r="O19">
+        <v>1829</v>
+      </c>
       <c r="P19">
         <v>30480</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B20" s="1" t="s">
-        <v>97</v>
+        <v>61</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D20" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H20">
         <v>1219</v>
@@ -1271,15 +1239,15 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D21" s="2">
-        <v>4.5</v>
+        <v>15</v>
       </c>
       <c r="N21">
         <v>1524</v>
@@ -1288,146 +1256,143 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B22" s="1" t="s">
-        <v>57</v>
+        <v>101</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D22" s="2">
-        <v>8.5</v>
-      </c>
-      <c r="N22">
-        <v>1524</v>
+        <v>99</v>
+      </c>
+      <c r="H22">
+        <v>1219</v>
       </c>
       <c r="P22">
         <v>30480</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>41</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D23" s="2">
-        <v>99</v>
-      </c>
-      <c r="M23">
-        <v>1500</v>
+        <v>5</v>
+      </c>
+      <c r="N23">
+        <v>1524</v>
       </c>
       <c r="P23">
-        <v>50000</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
+        <v>30480</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>41</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>58</v>
+        <v>8</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D24" s="2">
+        <v>4</v>
+      </c>
+      <c r="N24">
+        <v>1524</v>
+      </c>
+      <c r="P24">
+        <v>30480</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B25" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D25" s="2">
+        <v>4</v>
+      </c>
+      <c r="N25">
+        <v>1524</v>
+      </c>
+      <c r="P25">
+        <v>30480</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B26" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D26" s="2">
+        <v>5</v>
+      </c>
+      <c r="N26">
+        <v>1524</v>
+      </c>
+      <c r="P26">
+        <v>30480</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B27" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D27" s="2">
+        <v>4</v>
+      </c>
+      <c r="N27">
+        <v>1524</v>
+      </c>
+      <c r="P27">
+        <v>30480</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B28" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N24">
-        <v>1524</v>
-      </c>
-      <c r="P24">
-        <v>30480</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B25" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D25" s="2">
-        <v>7</v>
-      </c>
-      <c r="N25">
-        <v>1524</v>
-      </c>
-      <c r="O25">
-        <v>1829</v>
-      </c>
-      <c r="P25">
-        <v>30480</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B26" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D26" s="2">
-        <v>25</v>
-      </c>
-      <c r="N26">
-        <v>1524</v>
-      </c>
-      <c r="P26">
-        <v>30480</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B27" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D27" s="2">
-        <v>5</v>
-      </c>
-      <c r="N27">
-        <v>1524</v>
-      </c>
-      <c r="P27">
-        <v>30480</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B28" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="C28" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D28" s="8">
-        <v>99</v>
-      </c>
-      <c r="H28">
-        <v>1219</v>
+      <c r="D28" s="2">
+        <v>10</v>
+      </c>
+      <c r="N28">
+        <v>1524</v>
       </c>
       <c r="P28">
         <v>30480</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>41</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D29" s="2">
-        <v>55</v>
+        <v>5</v>
       </c>
       <c r="N29">
         <v>1524</v>
@@ -1436,24 +1401,18 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B30" s="9" t="s">
-        <v>59</v>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B30" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D30" s="7">
-        <v>10.5</v>
-      </c>
-      <c r="H30">
-        <v>1219</v>
+      <c r="D30" s="2">
+        <v>5</v>
       </c>
       <c r="N30">
         <v>1524</v>
-      </c>
-      <c r="O30">
-        <v>1829</v>
       </c>
       <c r="P30">
         <v>30480</v>
@@ -1462,39 +1421,33 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B31" s="1" t="s">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D31" s="2">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="N31">
         <v>1524</v>
       </c>
-      <c r="O31">
-        <v>1829</v>
-      </c>
       <c r="P31">
         <v>30480</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B32" s="1" t="s">
-        <v>61</v>
+        <v>16</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D32" s="8">
+      <c r="D32" s="2">
         <v>4</v>
       </c>
-      <c r="H32">
-        <v>1219</v>
-      </c>
       <c r="N32">
         <v>1524</v>
       </c>
@@ -1502,18 +1455,18 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
         <v>41</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>62</v>
+        <v>17</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D33" s="2">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="N33">
         <v>1524</v>
@@ -1522,32 +1475,32 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B34" s="1" t="s">
-        <v>101</v>
+        <v>18</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D34" s="8">
-        <v>99</v>
-      </c>
-      <c r="H34">
-        <v>1219</v>
+      <c r="D34" s="2">
+        <v>4</v>
+      </c>
+      <c r="N34">
+        <v>1524</v>
       </c>
       <c r="P34">
         <v>30480</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B35" s="1" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D35" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N35">
         <v>1524</v>
@@ -1556,118 +1509,124 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B36" s="1" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D36" s="2">
+        <v>9.5</v>
+      </c>
+      <c r="J36">
+        <v>1260</v>
+      </c>
+      <c r="P36">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B37" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D37" s="2">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>1260</v>
+      </c>
+      <c r="P37">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B38" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D38" s="2">
+        <v>30.5</v>
+      </c>
+      <c r="N38">
+        <v>1524</v>
+      </c>
+      <c r="O38">
+        <v>1829</v>
+      </c>
+      <c r="P38">
+        <v>30480</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B39" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D39" s="2">
+        <v>54</v>
+      </c>
+      <c r="N39">
+        <v>1524</v>
+      </c>
+      <c r="P39">
+        <v>30480</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B40" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D40" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="N40">
+        <v>1524</v>
+      </c>
+      <c r="O40">
+        <v>1829</v>
+      </c>
+      <c r="P40">
+        <v>30480</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B41" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D41" s="2">
         <v>4</v>
       </c>
-      <c r="N36">
-        <v>1524</v>
-      </c>
-      <c r="P36">
-        <v>30480</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="B37" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D37" s="2">
+      <c r="N41">
+        <v>1524</v>
+      </c>
+      <c r="P41">
+        <v>30480</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B42" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D42" s="2">
         <v>4</v>
       </c>
-      <c r="N37">
-        <v>1524</v>
-      </c>
-      <c r="P37">
-        <v>30480</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="B38" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D38" s="2">
-        <v>5</v>
-      </c>
-      <c r="N38">
-        <v>1524</v>
-      </c>
-      <c r="P38">
-        <v>30480</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="B39" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D39" s="2">
-        <v>4</v>
-      </c>
-      <c r="N39">
-        <v>1524</v>
-      </c>
-      <c r="P39">
-        <v>30480</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="B40" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D40" s="2">
-        <v>10</v>
-      </c>
-      <c r="N40">
-        <v>1524</v>
-      </c>
-      <c r="P40">
-        <v>30480</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="B41" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D41" s="2">
-        <v>5</v>
-      </c>
-      <c r="N41">
-        <v>1524</v>
-      </c>
-      <c r="P41">
-        <v>30480</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="B42" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D42" s="2">
-        <v>5</v>
-      </c>
       <c r="N42">
         <v>1524</v>
       </c>
@@ -1675,18 +1634,18 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
         <v>41</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D43" s="2">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="N43">
         <v>1524</v>
@@ -1695,268 +1654,298 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B44" s="1" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D44" s="2">
-        <v>4</v>
-      </c>
-      <c r="N44">
-        <v>1524</v>
+        <v>8.5</v>
+      </c>
+      <c r="F44">
+        <v>1000</v>
+      </c>
+      <c r="J44">
+        <v>1260</v>
       </c>
       <c r="P44">
-        <v>30480</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.2">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B45" s="1" t="s">
-        <v>17</v>
+        <v>63</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D45" s="2">
+        <v>19.5</v>
+      </c>
+      <c r="N45">
+        <v>1524</v>
+      </c>
+      <c r="P45">
+        <v>30480</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B46" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D46" s="2">
+        <v>6</v>
+      </c>
+      <c r="N46">
+        <v>1524</v>
+      </c>
+      <c r="P46">
+        <v>30480</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B47" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D47" s="2">
+        <v>6.5</v>
+      </c>
+      <c r="N47">
+        <v>1524</v>
+      </c>
+      <c r="P47">
+        <v>30480</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B48" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D48" s="2">
+        <v>6.5</v>
+      </c>
+      <c r="N48">
+        <v>1524</v>
+      </c>
+      <c r="P48">
+        <v>30480</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B49" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D49" s="2">
         <v>5</v>
       </c>
-      <c r="N45">
-        <v>1524</v>
-      </c>
-      <c r="P45">
-        <v>30480</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="B46" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D46" s="2">
-        <v>4</v>
-      </c>
-      <c r="N46">
-        <v>1524</v>
-      </c>
-      <c r="P46">
-        <v>30480</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="B47" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D47" s="2">
-        <v>4</v>
-      </c>
-      <c r="N47">
-        <v>1524</v>
-      </c>
-      <c r="P47">
-        <v>30480</v>
-      </c>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="B48" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D48" s="2">
-        <v>9.5</v>
-      </c>
-      <c r="J48">
-        <v>1260</v>
-      </c>
-      <c r="P48">
-        <v>50000</v>
-      </c>
-    </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="B49" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D49" s="2">
-        <v>0</v>
-      </c>
-      <c r="J49">
-        <v>1260</v>
+      <c r="N49">
+        <v>1524</v>
       </c>
       <c r="P49">
-        <v>50000</v>
-      </c>
-    </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.2">
+        <v>30480</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B50" s="1" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D50" s="2">
-        <v>30.5</v>
+        <v>5</v>
       </c>
       <c r="N50">
         <v>1524</v>
       </c>
-      <c r="O50">
-        <v>1829</v>
-      </c>
       <c r="P50">
         <v>30480</v>
       </c>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
         <v>41</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D51" s="2">
-        <v>54</v>
-      </c>
-      <c r="N51">
-        <v>1524</v>
+        <v>4.5</v>
+      </c>
+      <c r="L51">
+        <v>1370</v>
       </c>
       <c r="P51">
-        <v>30480</v>
-      </c>
-    </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.2">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B52" s="1" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D52" s="2">
-        <v>2.5</v>
+        <v>16</v>
       </c>
       <c r="N52">
         <v>1524</v>
       </c>
-      <c r="O52">
+      <c r="P52">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B53" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D53" s="2">
+        <v>46</v>
+      </c>
+      <c r="E53">
+        <v>914</v>
+      </c>
+      <c r="N53">
+        <v>1524</v>
+      </c>
+      <c r="O53">
         <v>1829</v>
       </c>
-      <c r="P52">
-        <v>30480</v>
-      </c>
-    </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="B53" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D53" s="2">
-        <v>4</v>
-      </c>
-      <c r="N53">
-        <v>1524</v>
-      </c>
       <c r="P53">
         <v>30480</v>
       </c>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B54" s="1" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D54" s="2">
-        <v>4</v>
+        <v>46</v>
+      </c>
+      <c r="E54">
+        <v>914</v>
+      </c>
+      <c r="H54" s="8">
+        <v>1219</v>
       </c>
       <c r="N54">
         <v>1524</v>
       </c>
+      <c r="O54">
+        <v>1829</v>
+      </c>
       <c r="P54">
         <v>30480</v>
       </c>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
         <v>41</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D55" s="2">
-        <v>4</v>
+        <v>46</v>
+      </c>
+      <c r="E55">
+        <v>914</v>
+      </c>
+      <c r="H55">
+        <v>1219</v>
       </c>
       <c r="N55">
         <v>1524</v>
       </c>
+      <c r="O55">
+        <v>1829</v>
+      </c>
       <c r="P55">
         <v>30480</v>
       </c>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B56" s="1" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D56" s="2">
-        <v>8.5</v>
-      </c>
-      <c r="F56">
-        <v>1000</v>
-      </c>
-      <c r="J56">
-        <v>1260</v>
+        <v>45</v>
+      </c>
+      <c r="E56">
+        <v>914</v>
+      </c>
+      <c r="N56">
+        <v>1524</v>
+      </c>
+      <c r="O56">
+        <v>1829</v>
       </c>
       <c r="P56">
-        <v>50000</v>
-      </c>
-    </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.2">
+        <v>30480</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B57" s="1" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D57" s="2">
-        <v>19.5</v>
+        <v>37</v>
+      </c>
+      <c r="E57">
+        <v>914</v>
       </c>
       <c r="N57">
         <v>1524</v>
       </c>
+      <c r="O57">
+        <v>1829</v>
+      </c>
       <c r="P57">
         <v>30480</v>
       </c>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B58" s="1" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D58" s="2">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="N58">
         <v>1524</v>
@@ -1965,126 +1954,144 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
         <v>41</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D59" s="2">
-        <v>6.5</v>
+        <v>14.5</v>
+      </c>
+      <c r="H59">
+        <v>1219</v>
       </c>
       <c r="N59">
         <v>1524</v>
       </c>
+      <c r="O59">
+        <v>1829</v>
+      </c>
       <c r="P59">
         <v>30480</v>
       </c>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B60" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D60" s="2">
-        <v>6.5</v>
+        <v>14.5</v>
+      </c>
+      <c r="H60">
+        <v>1219</v>
       </c>
       <c r="N60">
         <v>1524</v>
       </c>
+      <c r="O60">
+        <v>1829</v>
+      </c>
       <c r="P60">
         <v>30480</v>
       </c>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B61" s="1" t="s">
-        <v>29</v>
+        <v>69</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D61" s="2">
+        <v>14.5</v>
+      </c>
+      <c r="H61">
+        <v>1219</v>
+      </c>
+      <c r="N61">
+        <v>1524</v>
+      </c>
+      <c r="O61">
+        <v>1829</v>
+      </c>
+      <c r="P61">
+        <v>30480</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B62" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D62" s="2">
         <v>5</v>
       </c>
-      <c r="N61">
-        <v>1524</v>
-      </c>
-      <c r="P61">
-        <v>30480</v>
-      </c>
-    </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="B62" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D62" s="2">
-        <v>4.5</v>
-      </c>
-      <c r="L62">
-        <v>1370</v>
+      <c r="N62">
+        <v>1524</v>
       </c>
       <c r="P62">
-        <v>25000</v>
-      </c>
-    </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.2">
+        <v>30480</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B63" s="1" t="s">
-        <v>31</v>
+        <v>70</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D63" s="8">
-        <v>16</v>
+      <c r="D63" s="2">
+        <v>11</v>
+      </c>
+      <c r="H63">
+        <v>1219</v>
       </c>
       <c r="N63">
         <v>1524</v>
       </c>
+      <c r="O63">
+        <v>1829</v>
+      </c>
       <c r="P63">
-        <v>50000</v>
-      </c>
-    </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.2">
+        <v>30480</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B64" s="1" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D64" s="2">
-        <v>14.5</v>
-      </c>
-      <c r="H64">
-        <v>1219</v>
+        <v>5</v>
       </c>
       <c r="N64">
         <v>1524</v>
       </c>
-      <c r="O64">
-        <v>1829</v>
-      </c>
       <c r="P64">
         <v>30480</v>
       </c>
     </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B65" s="1" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D65" s="2">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="H65">
         <v>1219</v>
@@ -2099,164 +2106,161 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B66" s="1" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D66" s="2">
-        <v>14.5</v>
-      </c>
-      <c r="H66">
+        <v>6</v>
+      </c>
+      <c r="N66">
+        <v>1524</v>
+      </c>
+      <c r="P66">
+        <v>30480</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B67" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D67" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="N67">
+        <v>1524</v>
+      </c>
+      <c r="P67">
+        <v>30480</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B68" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D68" s="2">
+        <v>19</v>
+      </c>
+      <c r="H68">
         <v>1219</v>
       </c>
-      <c r="N66">
-        <v>1524</v>
-      </c>
-      <c r="O66">
+      <c r="N68">
+        <v>1524</v>
+      </c>
+      <c r="P68">
+        <v>30480</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B69" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D69" s="2">
+        <v>30</v>
+      </c>
+      <c r="N69">
+        <v>1524</v>
+      </c>
+      <c r="P69">
+        <v>30480</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B70" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D70" s="2">
+        <v>21.5</v>
+      </c>
+      <c r="E70">
+        <v>914</v>
+      </c>
+      <c r="N70">
+        <v>1524</v>
+      </c>
+      <c r="O70">
         <v>1829</v>
       </c>
-      <c r="P66">
-        <v>30480</v>
-      </c>
-    </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="B67" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D67" s="8">
-        <v>11</v>
-      </c>
-      <c r="H67">
-        <v>1219</v>
-      </c>
-      <c r="N67">
-        <v>1524</v>
-      </c>
-      <c r="O67">
+      <c r="P70">
+        <v>30480</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B71" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D71" s="2">
+        <v>21.5</v>
+      </c>
+      <c r="K71">
+        <v>1270</v>
+      </c>
+      <c r="N71">
+        <v>1524</v>
+      </c>
+      <c r="P71">
+        <v>30480</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B72" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D72" s="2">
+        <v>19.5</v>
+      </c>
+      <c r="O72">
         <v>1829</v>
       </c>
-      <c r="P67">
-        <v>30480</v>
-      </c>
-    </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="B68" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D68" s="2">
-        <v>5</v>
-      </c>
-      <c r="N68">
-        <v>1524</v>
-      </c>
-      <c r="P68">
-        <v>30480</v>
-      </c>
-    </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="B69" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D69" s="8">
-        <v>11</v>
-      </c>
-      <c r="H69">
-        <v>1219</v>
-      </c>
-      <c r="N69">
-        <v>1524</v>
-      </c>
-      <c r="O69">
+      <c r="P72">
+        <v>30480</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B73" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D73" s="2">
+        <v>12</v>
+      </c>
+      <c r="K73">
+        <v>1270</v>
+      </c>
+      <c r="N73">
+        <v>1524</v>
+      </c>
+      <c r="O73">
         <v>1829</v>
       </c>
-      <c r="P69">
-        <v>30480</v>
-      </c>
-    </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="B70" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D70" s="2">
-        <v>5</v>
-      </c>
-      <c r="N70">
-        <v>1524</v>
-      </c>
-      <c r="P70">
-        <v>30480</v>
-      </c>
-    </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="B71" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D71" s="2">
-        <v>7.5</v>
-      </c>
-      <c r="N71">
-        <v>1524</v>
-      </c>
-      <c r="P71">
-        <v>30480</v>
-      </c>
-    </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="B72" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D72" s="2">
-        <v>6</v>
-      </c>
-      <c r="N72">
-        <v>1524</v>
-      </c>
-      <c r="P72">
-        <v>30480</v>
-      </c>
-    </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="B73" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D73" s="2">
-        <v>19</v>
-      </c>
-      <c r="H73">
-        <v>1219</v>
-      </c>
-      <c r="N73">
-        <v>1524</v>
-      </c>
       <c r="P73">
         <v>30480</v>
       </c>
     </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B74" s="1" t="s">
         <v>77</v>
       </c>
@@ -2276,7 +2280,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B75" s="1" t="s">
         <v>78</v>
       </c>
@@ -2299,7 +2303,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B76" s="1" t="s">
         <v>79</v>
       </c>
@@ -2319,7 +2323,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B77" s="1" t="s">
         <v>80</v>
       </c>
@@ -2336,7 +2340,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B78" s="1" t="s">
         <v>81</v>
       </c>
@@ -2353,7 +2357,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B79" s="1" t="s">
         <v>32</v>
       </c>
@@ -2370,7 +2374,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
         <v>41</v>
       </c>
@@ -2390,47 +2394,47 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B81" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D81" s="2">
+        <v>11</v>
+      </c>
+      <c r="H81">
+        <v>1219</v>
+      </c>
+      <c r="N81">
+        <v>1524</v>
+      </c>
+      <c r="O81">
+        <v>1829</v>
+      </c>
+      <c r="P81">
+        <v>30480</v>
+      </c>
+    </row>
+    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B82" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="C81" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D81" s="2">
+      <c r="C82" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D82" s="2">
         <v>6.5</v>
       </c>
-      <c r="N81">
-        <v>1524</v>
-      </c>
-      <c r="P81">
-        <v>30480</v>
-      </c>
-    </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="B82" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D82" s="8">
-        <v>11</v>
-      </c>
-      <c r="H82">
-        <v>1219</v>
-      </c>
       <c r="N82">
         <v>1524</v>
       </c>
-      <c r="O82">
-        <v>1829</v>
-      </c>
       <c r="P82">
         <v>30480</v>
       </c>
     </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A83" s="5" t="s">
         <v>41</v>
       </c>
@@ -2450,33 +2454,36 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B84" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D84" s="2">
+        <v>4</v>
+      </c>
+      <c r="N84">
+        <v>1524</v>
+      </c>
+      <c r="P84">
+        <v>30480</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A85" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B85" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C84" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D84" s="2">
+      <c r="C85" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D85" s="2">
         <v>8.5</v>
       </c>
-      <c r="N84">
-        <v>1524</v>
-      </c>
-      <c r="P84">
-        <v>30480</v>
-      </c>
-    </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="B85" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D85" s="2">
-        <v>4</v>
-      </c>
       <c r="N85">
         <v>1524</v>
       </c>
@@ -2484,7 +2491,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B86" s="1" t="s">
         <v>85</v>
       </c>
@@ -2504,7 +2511,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B87" s="1" t="s">
         <v>86</v>
       </c>
@@ -2524,7 +2531,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A88" s="5" t="s">
         <v>41</v>
       </c>
@@ -2544,51 +2551,51 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B89" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D89" s="2">
+        <v>10.5</v>
+      </c>
+      <c r="N89">
+        <v>1524</v>
+      </c>
+      <c r="O89">
+        <v>1829</v>
+      </c>
+      <c r="P89">
+        <v>30480</v>
+      </c>
+    </row>
+    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B90" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C89" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D89" s="8">
+      <c r="C90" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D90" s="2">
         <v>13</v>
       </c>
-      <c r="N89">
-        <v>1524</v>
-      </c>
-      <c r="P89">
-        <v>30480</v>
-      </c>
-    </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="B90" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C90" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D90" s="8">
-        <v>10.5</v>
-      </c>
       <c r="N90">
         <v>1524</v>
       </c>
-      <c r="O90">
-        <v>1829</v>
-      </c>
       <c r="P90">
         <v>30480</v>
       </c>
     </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B91" s="1" t="s">
         <v>89</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D91" s="8">
+      <c r="D91" s="2">
         <v>10.5</v>
       </c>
       <c r="N91">
@@ -2601,14 +2608,14 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B92" s="1" t="s">
         <v>90</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D92" s="8">
+      <c r="D92" s="2">
         <v>9</v>
       </c>
       <c r="N92">
@@ -2618,7 +2625,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A93" s="5" t="s">
         <v>41</v>
       </c>
@@ -2638,7 +2645,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B94" s="1" t="s">
         <v>91</v>
       </c>
@@ -2655,7 +2662,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B95" s="1" t="s">
         <v>34</v>
       </c>
@@ -2672,7 +2679,7 @@
         <v>25000</v>
       </c>
     </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B96" s="1" t="s">
         <v>35</v>
       </c>
@@ -2689,7 +2696,7 @@
         <v>25000</v>
       </c>
     </row>
-    <row r="97" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="97" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B97" s="1" t="s">
         <v>36</v>
       </c>
@@ -2709,7 +2716,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="98" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="98" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B98" s="1" t="s">
         <v>37</v>
       </c>
@@ -2729,14 +2736,14 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="99" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="99" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B99" s="1" t="s">
         <v>38</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D99" s="8">
+      <c r="D99" s="2">
         <v>10</v>
       </c>
       <c r="N99">
@@ -2746,7 +2753,7 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="100" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="100" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B100" s="1" t="s">
         <v>93</v>
       </c>
@@ -2764,6 +2771,9 @@
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B4:P100">
+    <sortCondition ref="B4:B100"/>
+  </sortState>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <pageSetup scale="70" fitToHeight="0" orientation="portrait" r:id="rId1"/>
   <headerFooter>
